--- a/data/2026_WOP_cross_selections.xlsx
+++ b/data/2026_WOP_cross_selections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pth7\Documents\Intercrop JLJ\2026_winter\2026_winter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F15E467-6E8A-43FC-B894-0DFD3B107C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E44B3B5-0695-4D95-BBEC-A925FE82F020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1404" yWindow="0" windowWidth="21732" windowHeight="12336" xr2:uid="{CA3C6CF0-F642-4D41-8DBA-D6CDE9A2A3DF}"/>
+    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{CA3C6CF0-F642-4D41-8DBA-D6CDE9A2A3DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
